--- a/lab2_ktpm_quocphong_1150080153_11cnpm2.xlsx
+++ b/lab2_ktpm_quocphong_1150080153_11cnpm2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="5090" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="5090" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Bài 1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,8 @@
     <sheet name="Bài 3" sheetId="4" r:id="rId3"/>
     <sheet name="Bài 4" sheetId="5" r:id="rId4"/>
     <sheet name="Bài 5" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet name="Bài 6" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="115">
   <si>
     <t>Test case ID</t>
   </si>
@@ -329,6 +330,54 @@
   </si>
   <si>
     <t>150 (Vùng hợp lệ: 141-200, mong đợi giá vé 300000).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thiết kế testcase cho ô text chỉ cho nhập số nguyên với độ dài [1-10] hoặc [20-30]</t>
+  </si>
+  <si>
+    <t>Vùng hợp lệ: Độ dài 1-10, số nguyên</t>
+  </si>
+  <si>
+    <t>Vùng hợp lệ: Độ dài 20-30, số nguyên</t>
+  </si>
+  <si>
+    <t>Vùng không hợp lệ: Độ dài &lt;1 hoặc 11-19 hoặc &gt;30 hoặc không phải số</t>
+  </si>
+  <si>
+    <t>1 &lt;= Độ dài &lt;= 10</t>
+  </si>
+  <si>
+    <t>11 &lt;= Độ dài &lt;= 19</t>
+  </si>
+  <si>
+    <t>20 &lt;= Độ dài &lt;= 30</t>
+  </si>
+  <si>
+    <t>Độ dài &gt;30</t>
+  </si>
+  <si>
+    <t>Không phải số</t>
+  </si>
+  <si>
+    <t>Test Case 1: Độ dài dưới 1</t>
+  </si>
+  <si>
+    <t>(rỗng)</t>
+  </si>
+  <si>
+    <t>Test Case 2: Độ dài 1-10</t>
+  </si>
+  <si>
+    <t>Test Case 3: Độ dài 11-19</t>
+  </si>
+  <si>
+    <t>Test Case 4: Độ dài 20-30</t>
+  </si>
+  <si>
+    <t>Test Case 5: Độ dài trên 30</t>
+  </si>
+  <si>
+    <t>abcdef</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1137,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="C15" s="10" t="s">
         <v>39</v>
       </c>
@@ -1097,7 +1146,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="3:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1133,7 +1182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C24" s="3" t="s">
         <v>23</v>
       </c>
@@ -1141,7 +1190,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="3:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C25" s="3" t="s">
         <v>26</v>
       </c>
@@ -1149,7 +1198,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="3:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1157,7 +1206,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="3:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C27" s="3" t="s">
         <v>30</v>
       </c>
@@ -1165,7 +1214,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="3:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C28" s="3" t="s">
         <v>45</v>
       </c>
@@ -2025,6 +2074,300 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="5" width="27.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="9">
+        <v>46028</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>1</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="D10" s="6">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="D11" s="6">
+        <v>3</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>4</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="D12" s="6">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="3">
+        <v>12345</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="3">
+        <v>12345678901</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1.23456789012345E+19</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1.23456789012345E+30</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C30" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
